--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.1239565724525</v>
+        <v>4.245142943023532</v>
       </c>
       <c r="D2" t="n">
-        <v>25.84787102900149</v>
+        <v>4.200279042212743</v>
       </c>
       <c r="E2" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F2" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.07380065953926</v>
+        <v>3.424492607175129</v>
       </c>
       <c r="D3" t="n">
-        <v>20.96016151658909</v>
+        <v>3.406026246445727</v>
       </c>
       <c r="E3" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F3" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.094002122358</v>
+        <v>4.077775344883175</v>
       </c>
       <c r="D4" t="n">
-        <v>24.7119393933608</v>
+        <v>4.01569015142113</v>
       </c>
       <c r="E4" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F4" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.27304012345918</v>
+        <v>8.169369020062117</v>
       </c>
       <c r="D5" t="n">
-        <v>50.08377688562746</v>
+        <v>8.138613743914464</v>
       </c>
       <c r="E5" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F5" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.4659964721261</v>
+        <v>4.625724426720491</v>
       </c>
       <c r="D6" t="n">
-        <v>28.68666158264285</v>
+        <v>4.661582507179462</v>
       </c>
       <c r="E6" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F6" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.85615727215932</v>
+        <v>3.389125556725889</v>
       </c>
       <c r="D7" t="n">
-        <v>19.85325421664732</v>
+        <v>3.22615381020519</v>
       </c>
       <c r="E7" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F7" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.83461412092681</v>
+        <v>3.548124794650606</v>
       </c>
       <c r="D8" t="n">
-        <v>22.0473690432076</v>
+        <v>3.582697469521235</v>
       </c>
       <c r="E8" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F8" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.852904985011918</v>
+        <v>1.276097060064437</v>
       </c>
       <c r="D9" t="n">
-        <v>8.655974793643514</v>
+        <v>1.406595903967071</v>
       </c>
       <c r="E9" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F9" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.60916198730583</v>
+        <v>3.511488822937198</v>
       </c>
       <c r="D10" t="n">
-        <v>22.52153916466265</v>
+        <v>3.659750114257681</v>
       </c>
       <c r="E10" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F10" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.74768232245806</v>
+        <v>4.183998377399435</v>
       </c>
       <c r="D11" t="n">
-        <v>25.75479004999607</v>
+        <v>4.185153383124362</v>
       </c>
       <c r="E11" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F11" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.08456037846301</v>
+        <v>3.263741061500239</v>
       </c>
       <c r="D12" t="n">
-        <v>20.69499839609174</v>
+        <v>3.362937239364908</v>
       </c>
       <c r="E12" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F12" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.94813135902544</v>
+        <v>4.216571345841634</v>
       </c>
       <c r="D13" t="n">
-        <v>26.70154919289887</v>
+        <v>4.339001743846067</v>
       </c>
       <c r="E13" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F13" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.702228025100704</v>
+        <v>1.251612054078864</v>
       </c>
       <c r="D14" t="n">
-        <v>7.869200917030146</v>
+        <v>1.278745149017399</v>
       </c>
       <c r="E14" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F14" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.62645139815782</v>
+        <v>2.376798352200645</v>
       </c>
       <c r="D15" t="n">
-        <v>14.66764904131249</v>
+        <v>2.38349296921328</v>
       </c>
       <c r="E15" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F15" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.47485900696797</v>
+        <v>3.977164588632295</v>
       </c>
       <c r="D16" t="n">
-        <v>24.63858531855219</v>
+        <v>4.003770114264731</v>
       </c>
       <c r="E16" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F16" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.67479719575733</v>
+        <v>3.359654544310567</v>
       </c>
       <c r="D17" t="n">
-        <v>20.47890968649951</v>
+        <v>3.327822824056171</v>
       </c>
       <c r="E17" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F17" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>23.29395424985872</v>
+        <v>3.785267565602042</v>
       </c>
       <c r="D18" t="n">
-        <v>23.49710059772372</v>
+        <v>3.818278847130105</v>
       </c>
       <c r="E18" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F18" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>26.62950368249486</v>
+        <v>4.327294348405415</v>
       </c>
       <c r="D19" t="n">
-        <v>32.824642162588</v>
+        <v>5.33400435142055</v>
       </c>
       <c r="E19" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F19" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>36.56813384441089</v>
+        <v>5.942321749716769</v>
       </c>
       <c r="D20" t="n">
-        <v>36.79502323135767</v>
+        <v>5.979191275095622</v>
       </c>
       <c r="E20" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F20" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>10.48668907077577</v>
+        <v>1.704086974001062</v>
       </c>
       <c r="D21" t="n">
-        <v>10.57657239509144</v>
+        <v>1.71869301420236</v>
       </c>
       <c r="E21" t="n">
-        <v>9.271607752851766</v>
+        <v>1.506636259838412</v>
       </c>
       <c r="F21" t="n">
-        <v>9.407959408950415</v>
+        <v>1.528793403954442</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
